--- a/工具 tools/概率计算/常见概率.xlsx
+++ b/工具 tools/概率计算/常见概率.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\常用\概率\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\工具 tools\概率计算\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61A832B-4443-4311-84E6-99022DED7904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FBFF8E0-A2A9-47B5-8ABF-179D84759F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2500" yWindow="2500" windowWidth="19200" windowHeight="10060" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="普通类" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="降水类" sheetId="4" r:id="rId3"/>
     <sheet name="甘蔗类" sheetId="3" r:id="rId4"/>
     <sheet name="海带类" sheetId="2" r:id="rId5"/>
+    <sheet name="掠夺三" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="80">
   <si>
     <t>类</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -352,6 +353,12 @@
   <si>
     <t>铜门只有下半部分选中能氧化，但是统计周围的时候又包含上半部分</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常见掉落物掠夺加成：net.minecraft.world.level.storage.loot.functions.EnchantedCountIncreaseFunction#run</t>
+  </si>
+  <si>
+    <t>稀有掉落物掠夺加成：net.minecraft.world.level.storage.loot.predicates.LootItemRandomChanceWithEnchantedBonusCondition#test</t>
   </si>
 </sst>
 </file>
@@ -734,18 +741,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.9140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.25" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="80.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="3"/>
+    <col min="4" max="4" width="13.58203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.4140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="80.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.9140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -762,7 +769,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>46</v>
       </c>
@@ -783,7 +790,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>52</v>
       </c>
@@ -797,7 +804,7 @@
       <c r="E3" s="12"/>
       <c r="F3" s="14"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>47</v>
       </c>
@@ -811,7 +818,7 @@
       <c r="E4" s="12"/>
       <c r="F4" s="14"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>48</v>
       </c>
@@ -825,7 +832,7 @@
       <c r="E5" s="12"/>
       <c r="F5" s="14"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>50</v>
       </c>
@@ -839,7 +846,7 @@
       <c r="E6" s="12"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
@@ -857,7 +864,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
@@ -878,7 +885,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>18</v>
       </c>
@@ -899,7 +906,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
@@ -920,12 +927,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
@@ -938,7 +945,7 @@
         <v>0.17578125</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>6</v>
       </c>
@@ -956,7 +963,7 @@
         <v>0.17578125</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>5</v>
       </c>
@@ -974,12 +981,12 @@
         <v>5.859375E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>10</v>
       </c>
@@ -997,7 +1004,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>72</v>
       </c>
@@ -1015,7 +1022,7 @@
         <v>5.6888888888888892E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>73</v>
       </c>
@@ -1050,12 +1057,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA1D0F19-D9DA-4A78-8224-12F0CC5DB67A}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="78.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1069,7 +1076,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -1084,7 +1091,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>69</v>
       </c>
@@ -1108,16 +1115,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{803531CA-6398-4814-BAD9-953E9AD59F10}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.08203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.58203125" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="7"/>
+    <col min="5" max="16384" width="8.9140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1131,7 +1138,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>34</v>
       </c>
@@ -1139,7 +1146,7 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>35</v>
       </c>
@@ -1147,7 +1154,7 @@
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
@@ -1159,7 +1166,7 @@
       </c>
       <c r="D4" s="6"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
@@ -1180,17 +1187,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59110A14-25B8-461A-B682-E0D44E445B43}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="14.6640625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.58203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.4140625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="14.6640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1207,7 +1214,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>15</v>
       </c>
@@ -1222,7 +1229,7 @@
       </c>
       <c r="E2" s="6"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>16</v>
       </c>
@@ -1246,19 +1253,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88D36301-2C6C-4C74-9DAC-4C9131A94EAB}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.4140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.4140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.4140625" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="7"/>
-    <col min="7" max="7" width="21.5546875" style="7" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="7"/>
+    <col min="6" max="6" width="8.9140625" style="7"/>
+    <col min="7" max="7" width="21.58203125" style="7" customWidth="1"/>
+    <col min="8" max="16384" width="8.9140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1278,7 +1285,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>20</v>
       </c>
@@ -1299,7 +1306,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>19</v>
       </c>
@@ -1320,7 +1327,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>24</v>
       </c>
@@ -1341,7 +1348,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>25</v>
       </c>
@@ -1360,6 +1367,27 @@
       </c>
       <c r="G5" s="7" t="s">
         <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAACDFAA-1463-4F90-A325-E42723634C49}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
